--- a/informed_consent_forms/003_pedagogical_innovation_showcase_consent_form--informed_consent_forms.xlsx
+++ b/informed_consent_forms/003_pedagogical_innovation_showcase_consent_form--informed_consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>school_info_1</t>
+          <t>school_info_1_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>School Info 1 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>school_info_2</t>
+          <t>school_info_2_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Project Type</t>
+          <t>School Info 2 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Student Work</t>
+          <t>Student Work 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>student_work_2</t>
+          <t>student_work_2_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category (2)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>Project (3)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -940,9 +940,9 @@
   <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'school_a'}</t>
+          <t>school_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'School A'}</t>
+          <t>School A</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'school_b'}</t>
+          <t>school_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'School B'}</t>
+          <t>School B</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'school_c'}</t>
+          <t>school_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'School C'}</t>
+          <t>School C</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'project_a'}</t>
+          <t>project_a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Project A'}</t>
+          <t>Project A</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'project_b'}</t>
+          <t>project_b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Project B'}</t>
+          <t>Project B</t>
         </is>
       </c>
     </row>
@@ -1055,63 +1055,63 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'project_c'}</t>
+          <t>project_c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Project C'}</t>
+          <t>Project C</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>school_info_2_choices</t>
+          <t>school_info_2_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'project_type_a'}</t>
+          <t>project_type_a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Project Type A'}</t>
+          <t>Project Type A</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>school_info_2_choices</t>
+          <t>school_info_2_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'project_type_b'}</t>
+          <t>project_type_b</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Project Type B'}</t>
+          <t>Project Type B</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>school_info_2_choices</t>
+          <t>school_info_2_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'project_type_c'}</t>
+          <t>project_type_c</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Project Type C'}</t>
+          <t>Project Type C</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'student_work_a'}</t>
+          <t>student_work_a</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Student Work A'}</t>
+          <t>Student Work A</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'student_work_b'}</t>
+          <t>student_work_b</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Student Work B'}</t>
+          <t>Student Work B</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'student_work_c'}</t>
+          <t>student_work_c</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Student Work C'}</t>
+          <t>Student Work C</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'student_work_a'}</t>
+          <t>student_work_a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Student Work A'}</t>
+          <t>Student Work A</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'student_work_b'}</t>
+          <t>student_work_b</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Student Work B'}</t>
+          <t>Student Work B</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'student_work_c'}</t>
+          <t>student_work_c</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Student Work C'}</t>
+          <t>Student Work C</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'project_category_a'}</t>
+          <t>project_category_a</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Project Category A'}</t>
+          <t>Project Category A</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'project_category_b'}</t>
+          <t>project_category_b</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Project Category B'}</t>
+          <t>Project Category B</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'project_category_c'}</t>
+          <t>project_category_c</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Project Category C'}</t>
+          <t>Project Category C</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'category_a'}</t>
+          <t>category_a</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Category A'}</t>
+          <t>Category A</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'category_b'}</t>
+          <t>category_b</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Category B'}</t>
+          <t>Category B</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'category_c'}</t>
+          <t>category_c</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Category C'}</t>
+          <t>Category C</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
